--- a/docs/downloads/04/tbl_men_obs_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_men_obs_alaotra_tous.xlsx
@@ -369,7 +369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B2">
@@ -379,7 +379,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3">
@@ -389,7 +389,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B4">
@@ -399,7 +399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B5">
@@ -409,7 +409,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B6">
@@ -419,7 +419,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B7">
@@ -429,7 +429,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B8">
@@ -439,7 +439,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B9">
@@ -449,7 +449,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B10">
